--- a/development/one_file_rosetta_output/SP77956_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP77956_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E640"/>
+  <dimension ref="A1:F640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -482,7 +491,10 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -508,9 +520,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -571,9 +586,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -601,7 +619,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -629,7 +650,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -735,9 +759,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -791,9 +818,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -849,7 +879,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -905,7 +938,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -961,7 +997,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1024,7 +1063,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1087,7 +1129,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1115,7 +1160,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1178,7 +1226,10 @@
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1247,9 +1298,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1327,7 +1381,10 @@
       <c r="D18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1405,7 +1462,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1431,9 +1491,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1517,9 +1580,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1603,9 +1669,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1691,7 +1760,10 @@
       <c r="D23" s="4">
         <v>3</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4">
+        <v>3</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1775,9 +1847,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>5</v>
+      </c>
+      <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1868,9 +1943,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>5</v>
+      </c>
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1961,9 +2039,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>5</v>
+      </c>
+      <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2054,9 +2135,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>5</v>
+      </c>
+      <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2149,7 +2233,10 @@
       <c r="D28" s="4">
         <v>5</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4">
+        <v>5</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2240,9 +2327,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2333,9 +2423,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
         <v>2</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2426,9 +2519,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>6</v>
+      </c>
+      <c r="E31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2519,9 +2615,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>6</v>
+      </c>
+      <c r="E32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2612,9 +2711,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>6</v>
+      </c>
+      <c r="E33" s="4">
         <v>3</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2705,9 +2807,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2808,7 +2913,10 @@
       <c r="D35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2834,9 +2942,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2942,9 +3053,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4">
         <v>2</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3050,9 +3164,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>4</v>
+      </c>
+      <c r="E38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3158,9 +3275,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4">
         <v>2</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3266,9 +3386,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>4</v>
+      </c>
+      <c r="E40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3374,9 +3497,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4">
         <v>2</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3482,9 +3608,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>4</v>
+      </c>
+      <c r="E42" s="4">
         <v>3</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3590,9 +3719,12 @@
         </is>
       </c>
       <c r="D43" s="4">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3706,9 +3838,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>4</v>
+      </c>
+      <c r="E44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3824,7 +3959,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3852,7 +3990,10 @@
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3906,9 +4047,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3964,7 +4108,10 @@
       <c r="D48" s="4">
         <v>1</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4035,7 +4182,10 @@
       <c r="D49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4063,7 +4213,10 @@
       <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4141,7 +4294,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4227,7 +4383,10 @@
       <c r="D52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="4">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4255,7 +4414,10 @@
       <c r="D53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4346,9 +4508,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>4</v>
+      </c>
+      <c r="E54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4447,9 +4612,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4">
         <v>2</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4548,9 +4716,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>4</v>
+      </c>
+      <c r="E56" s="4">
         <v>3</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4651,7 +4822,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4750,9 +4924,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>3</v>
+      </c>
+      <c r="E58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4858,9 +5035,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>3</v>
+      </c>
+      <c r="E59" s="4">
         <v>2</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4966,9 +5146,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>2</v>
+      </c>
+      <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5076,7 +5259,10 @@
       <c r="D61" s="4">
         <v>2</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5184,7 +5370,10 @@
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5210,9 +5399,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>2</v>
+      </c>
+      <c r="E63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5328,7 +5520,10 @@
       <c r="D64" s="4">
         <v>2</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>2</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5444,7 +5639,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5472,7 +5670,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5526,9 +5727,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>2</v>
+      </c>
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5614,7 +5818,10 @@
       <c r="D68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>2</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5698,9 +5905,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>2</v>
+      </c>
+      <c r="E69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5784,9 +5994,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5872,7 +6085,10 @@
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5963,9 +6179,12 @@
         </is>
       </c>
       <c r="D72" s="4">
+        <v>2</v>
+      </c>
+      <c r="E72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6066,7 +6285,10 @@
       <c r="D73" s="4">
         <v>2</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>2</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6165,9 +6387,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>3</v>
+      </c>
+      <c r="E74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6195,7 +6420,10 @@
       <c r="D75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6303,7 +6531,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6329,9 +6560,12 @@
         </is>
       </c>
       <c r="D77" s="4">
+        <v>3</v>
+      </c>
+      <c r="E77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6445,9 +6679,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>3</v>
+      </c>
+      <c r="E78" s="4">
         <v>2</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6563,7 +6800,10 @@
       <c r="D79" s="4">
         <v>3</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>3</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6677,9 +6917,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6795,7 +7038,10 @@
       <c r="D81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6911,7 +7157,10 @@
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6939,7 +7188,10 @@
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6993,9 +7245,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>228</v>
+      </c>
+      <c r="E84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7056,9 +7311,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>228</v>
+      </c>
+      <c r="E85" s="4">
         <v>2</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7119,9 +7377,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>228</v>
+      </c>
+      <c r="E86" s="4">
         <v>3</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7182,9 +7443,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>228</v>
+      </c>
+      <c r="E87" s="4">
         <v>4</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7245,9 +7509,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>228</v>
+      </c>
+      <c r="E88" s="4">
         <v>5</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7308,9 +7575,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>33</v>
+      </c>
+      <c r="E89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7371,9 +7641,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>33</v>
+      </c>
+      <c r="E90" s="4">
         <v>2</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7434,9 +7707,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>33</v>
+      </c>
+      <c r="E91" s="4">
         <v>3</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7497,9 +7773,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>33</v>
+      </c>
+      <c r="E92" s="4">
         <v>4</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7560,9 +7839,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>33</v>
+      </c>
+      <c r="E93" s="4">
         <v>5</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7623,9 +7905,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>199</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7686,9 +7971,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>199</v>
+      </c>
+      <c r="E95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7749,9 +8037,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>199</v>
+      </c>
+      <c r="E96" s="4">
         <v>3</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7812,9 +8103,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>199</v>
+      </c>
+      <c r="E97" s="4">
         <v>4</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7875,9 +8169,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>199</v>
+      </c>
+      <c r="E98" s="4">
         <v>5</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7938,9 +8235,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>87</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8009,9 +8309,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>87</v>
+      </c>
+      <c r="E100" s="4">
         <v>2</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8080,9 +8383,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>87</v>
+      </c>
+      <c r="E101" s="4">
         <v>3</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8151,9 +8457,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>87</v>
+      </c>
+      <c r="E102" s="4">
         <v>4</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8222,9 +8531,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>87</v>
+      </c>
+      <c r="E103" s="4">
         <v>5</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8293,9 +8605,12 @@
         </is>
       </c>
       <c r="D104" s="4">
+        <v>8</v>
+      </c>
+      <c r="E104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8364,9 +8679,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>8</v>
+      </c>
+      <c r="E105" s="4">
         <v>2</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8435,9 +8753,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>8</v>
+      </c>
+      <c r="E106" s="4">
         <v>3</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8506,9 +8827,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>8</v>
+      </c>
+      <c r="E107" s="4">
         <v>4</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8577,9 +8901,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>8</v>
+      </c>
+      <c r="E108" s="4">
         <v>5</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8648,9 +8975,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>103</v>
+      </c>
+      <c r="E109" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8719,9 +9049,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>103</v>
+      </c>
+      <c r="E110" s="4">
         <v>2</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8790,9 +9123,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>103</v>
+      </c>
+      <c r="E111" s="4">
         <v>3</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8861,9 +9197,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>103</v>
+      </c>
+      <c r="E112" s="4">
         <v>4</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8932,9 +9271,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>103</v>
+      </c>
+      <c r="E113" s="4">
         <v>5</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9003,9 +9345,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>26</v>
+      </c>
+      <c r="E114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9081,9 +9426,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>26</v>
+      </c>
+      <c r="E115" s="4">
         <v>2</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9159,9 +9507,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>26</v>
+      </c>
+      <c r="E116" s="4">
         <v>3</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9237,9 +9588,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>26</v>
+      </c>
+      <c r="E117" s="4">
         <v>4</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9315,9 +9669,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>26</v>
+      </c>
+      <c r="E118" s="4">
         <v>5</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9393,9 +9750,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>6</v>
+      </c>
+      <c r="E119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9471,9 +9831,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>6</v>
+      </c>
+      <c r="E120" s="4">
         <v>2</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9549,9 +9912,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>6</v>
+      </c>
+      <c r="E121" s="4">
         <v>3</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9627,9 +9993,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>6</v>
+      </c>
+      <c r="E122" s="4">
         <v>4</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9705,9 +10074,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>6</v>
+      </c>
+      <c r="E123" s="4">
         <v>5</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9783,9 +10155,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>30</v>
+      </c>
+      <c r="E124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9861,9 +10236,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>30</v>
+      </c>
+      <c r="E125" s="4">
         <v>2</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9939,9 +10317,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>30</v>
+      </c>
+      <c r="E126" s="4">
         <v>3</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10017,9 +10398,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>30</v>
+      </c>
+      <c r="E127" s="4">
         <v>4</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10095,9 +10479,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>30</v>
+      </c>
+      <c r="E128" s="4">
         <v>5</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10173,9 +10560,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>12</v>
+      </c>
+      <c r="E129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10259,9 +10649,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>12</v>
+      </c>
+      <c r="E130" s="4">
         <v>2</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10345,9 +10738,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>12</v>
+      </c>
+      <c r="E131" s="4">
         <v>3</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10431,9 +10827,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>12</v>
+      </c>
+      <c r="E132" s="4">
         <v>4</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10517,9 +10916,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>12</v>
+      </c>
+      <c r="E133" s="4">
         <v>5</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10605,7 +11007,10 @@
       <c r="D134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="4">
+        <v>1</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10631,9 +11036,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>11</v>
+      </c>
+      <c r="E135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10717,9 +11125,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>11</v>
+      </c>
+      <c r="E136" s="4">
         <v>2</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10803,9 +11214,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>11</v>
+      </c>
+      <c r="E137" s="4">
         <v>3</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10889,9 +11303,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>11</v>
+      </c>
+      <c r="E138" s="4">
         <v>4</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10975,9 +11392,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>11</v>
+      </c>
+      <c r="E139" s="4">
         <v>5</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11061,9 +11481,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>6</v>
+      </c>
+      <c r="E140" s="4">
         <v>1</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11154,9 +11577,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>6</v>
+      </c>
+      <c r="E141" s="4">
         <v>2</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11249,7 +11675,10 @@
       <c r="D142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="4">
+        <v>1</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11277,7 +11706,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11376,9 +11808,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>141</v>
+      </c>
+      <c r="E144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11439,9 +11874,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>141</v>
+      </c>
+      <c r="E145" s="4">
         <v>2</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11502,9 +11940,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>141</v>
+      </c>
+      <c r="E146" s="4">
         <v>3</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11565,9 +12006,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>141</v>
+      </c>
+      <c r="E147" s="4">
         <v>4</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11628,9 +12072,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>141</v>
+      </c>
+      <c r="E148" s="4">
         <v>5</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11691,9 +12138,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>22</v>
+      </c>
+      <c r="E149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11754,9 +12204,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>22</v>
+      </c>
+      <c r="E150" s="4">
         <v>2</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11817,9 +12270,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>22</v>
+      </c>
+      <c r="E151" s="4">
         <v>3</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11880,9 +12336,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>22</v>
+      </c>
+      <c r="E152" s="4">
         <v>4</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11943,9 +12402,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>22</v>
+      </c>
+      <c r="E153" s="4">
         <v>5</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12006,9 +12468,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>215</v>
+      </c>
+      <c r="E154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12069,9 +12534,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>215</v>
+      </c>
+      <c r="E155" s="4">
         <v>2</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12132,9 +12600,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>215</v>
+      </c>
+      <c r="E156" s="4">
         <v>3</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12195,9 +12666,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>215</v>
+      </c>
+      <c r="E157" s="4">
         <v>4</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12258,9 +12732,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>215</v>
+      </c>
+      <c r="E158" s="4">
         <v>5</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12321,9 +12798,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>74</v>
+      </c>
+      <c r="E159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12392,9 +12872,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>74</v>
+      </c>
+      <c r="E160" s="4">
         <v>2</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12463,9 +12946,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>74</v>
+      </c>
+      <c r="E161" s="4">
         <v>3</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12534,9 +13020,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>74</v>
+      </c>
+      <c r="E162" s="4">
         <v>4</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12605,9 +13094,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>74</v>
+      </c>
+      <c r="E163" s="4">
         <v>5</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12676,9 +13168,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>11</v>
+      </c>
+      <c r="E164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12747,9 +13242,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>11</v>
+      </c>
+      <c r="E165" s="4">
         <v>2</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12818,9 +13316,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>11</v>
+      </c>
+      <c r="E166" s="4">
         <v>3</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12889,9 +13390,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>11</v>
+      </c>
+      <c r="E167" s="4">
         <v>4</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12960,9 +13464,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>11</v>
+      </c>
+      <c r="E168" s="4">
         <v>5</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13031,9 +13538,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>99</v>
+      </c>
+      <c r="E169" s="4">
         <v>1</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13102,9 +13612,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>99</v>
+      </c>
+      <c r="E170" s="4">
         <v>2</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13173,9 +13686,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>99</v>
+      </c>
+      <c r="E171" s="4">
         <v>3</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13244,9 +13760,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>99</v>
+      </c>
+      <c r="E172" s="4">
         <v>4</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13315,9 +13834,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>99</v>
+      </c>
+      <c r="E173" s="4">
         <v>5</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13386,9 +13908,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>21</v>
+      </c>
+      <c r="E174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13464,9 +13989,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>21</v>
+      </c>
+      <c r="E175" s="4">
         <v>2</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13542,9 +14070,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>21</v>
+      </c>
+      <c r="E176" s="4">
         <v>3</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13620,9 +14151,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>21</v>
+      </c>
+      <c r="E177" s="4">
         <v>4</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13698,9 +14232,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>21</v>
+      </c>
+      <c r="E178" s="4">
         <v>5</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13776,9 +14313,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>4</v>
+      </c>
+      <c r="E179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13804,9 +14344,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>28</v>
+      </c>
+      <c r="E180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13882,9 +14425,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>28</v>
+      </c>
+      <c r="E181" s="4">
         <v>2</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13960,9 +14506,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>28</v>
+      </c>
+      <c r="E182" s="4">
         <v>3</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14038,9 +14587,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>28</v>
+      </c>
+      <c r="E183" s="4">
         <v>4</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14116,9 +14668,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>28</v>
+      </c>
+      <c r="E184" s="4">
         <v>5</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14194,9 +14749,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>15</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14280,9 +14838,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>15</v>
+      </c>
+      <c r="E186" s="4">
         <v>2</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14366,9 +14927,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>15</v>
+      </c>
+      <c r="E187" s="4">
         <v>3</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14452,9 +15016,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>15</v>
+      </c>
+      <c r="E188" s="4">
         <v>4</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14538,9 +15105,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>15</v>
+      </c>
+      <c r="E189" s="4">
         <v>5</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14624,9 +15194,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14652,9 +15225,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>10</v>
+      </c>
+      <c r="E191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14738,9 +15314,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>10</v>
+      </c>
+      <c r="E192" s="4">
         <v>2</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14824,9 +15403,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>10</v>
+      </c>
+      <c r="E193" s="4">
         <v>3</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14910,9 +15492,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>10</v>
+      </c>
+      <c r="E194" s="4">
         <v>4</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14996,9 +15581,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>10</v>
+      </c>
+      <c r="E195" s="4">
         <v>5</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15082,9 +15670,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>2</v>
+      </c>
+      <c r="E196" s="4">
         <v>1</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15175,9 +15766,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>3</v>
+      </c>
+      <c r="E197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15270,7 +15864,10 @@
       <c r="D198" s="4">
         <v>1</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="4">
+        <v>1</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15324,9 +15921,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>170</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15387,9 +15987,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>170</v>
+      </c>
+      <c r="E200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15450,9 +16053,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>170</v>
+      </c>
+      <c r="E201" s="4">
         <v>3</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15513,9 +16119,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>170</v>
+      </c>
+      <c r="E202" s="4">
         <v>4</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15576,9 +16185,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>170</v>
+      </c>
+      <c r="E203" s="4">
         <v>5</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15639,9 +16251,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>24</v>
+      </c>
+      <c r="E204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15702,9 +16317,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>24</v>
+      </c>
+      <c r="E205" s="4">
         <v>2</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15765,9 +16383,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>24</v>
+      </c>
+      <c r="E206" s="4">
         <v>3</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15828,9 +16449,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>24</v>
+      </c>
+      <c r="E207" s="4">
         <v>4</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15891,9 +16515,12 @@
         </is>
       </c>
       <c r="D208" s="4">
+        <v>24</v>
+      </c>
+      <c r="E208" s="4">
         <v>5</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15954,9 +16581,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>210</v>
+      </c>
+      <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16017,9 +16647,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>210</v>
+      </c>
+      <c r="E210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16080,9 +16713,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>210</v>
+      </c>
+      <c r="E211" s="4">
         <v>3</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16143,9 +16779,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>210</v>
+      </c>
+      <c r="E212" s="4">
         <v>4</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16206,9 +16845,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>210</v>
+      </c>
+      <c r="E213" s="4">
         <v>5</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16269,9 +16911,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>108</v>
+      </c>
+      <c r="E214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16340,9 +16985,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>108</v>
+      </c>
+      <c r="E215" s="4">
         <v>2</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16411,9 +17059,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>108</v>
+      </c>
+      <c r="E216" s="4">
         <v>3</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16482,9 +17133,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>108</v>
+      </c>
+      <c r="E217" s="4">
         <v>4</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16553,9 +17207,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>108</v>
+      </c>
+      <c r="E218" s="4">
         <v>5</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16624,9 +17281,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>12</v>
+      </c>
+      <c r="E219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16695,9 +17355,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>12</v>
+      </c>
+      <c r="E220" s="4">
         <v>2</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16766,9 +17429,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>12</v>
+      </c>
+      <c r="E221" s="4">
         <v>3</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16837,9 +17503,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>12</v>
+      </c>
+      <c r="E222" s="4">
         <v>4</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16908,9 +17577,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>12</v>
+      </c>
+      <c r="E223" s="4">
         <v>5</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16979,9 +17651,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>132</v>
+      </c>
+      <c r="E224" s="4">
         <v>1</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17050,9 +17725,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>132</v>
+      </c>
+      <c r="E225" s="4">
         <v>2</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17121,9 +17799,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>132</v>
+      </c>
+      <c r="E226" s="4">
         <v>3</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17192,9 +17873,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>132</v>
+      </c>
+      <c r="E227" s="4">
         <v>4</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17263,9 +17947,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>132</v>
+      </c>
+      <c r="E228" s="4">
         <v>5</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17334,9 +18021,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>50</v>
+      </c>
+      <c r="E229" s="4">
         <v>1</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17412,9 +18102,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>50</v>
+      </c>
+      <c r="E230" s="4">
         <v>2</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17490,9 +18183,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>50</v>
+      </c>
+      <c r="E231" s="4">
         <v>3</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17568,9 +18264,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>50</v>
+      </c>
+      <c r="E232" s="4">
         <v>4</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17646,9 +18345,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>50</v>
+      </c>
+      <c r="E233" s="4">
         <v>5</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17724,9 +18426,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>7</v>
+      </c>
+      <c r="E234" s="4">
         <v>1</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17802,9 +18507,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>7</v>
+      </c>
+      <c r="E235" s="4">
         <v>2</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17880,9 +18588,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>7</v>
+      </c>
+      <c r="E236" s="4">
         <v>3</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17958,9 +18669,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>58</v>
+      </c>
+      <c r="E237" s="4">
         <v>1</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18036,9 +18750,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>58</v>
+      </c>
+      <c r="E238" s="4">
         <v>2</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18114,9 +18831,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>58</v>
+      </c>
+      <c r="E239" s="4">
         <v>3</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18192,9 +18912,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>58</v>
+      </c>
+      <c r="E240" s="4">
         <v>4</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18270,9 +18993,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>58</v>
+      </c>
+      <c r="E241" s="4">
         <v>5</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18348,9 +19074,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>12</v>
+      </c>
+      <c r="E242" s="4">
         <v>1</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18434,9 +19163,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>12</v>
+      </c>
+      <c r="E243" s="4">
         <v>2</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18520,9 +19252,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>12</v>
+      </c>
+      <c r="E244" s="4">
         <v>3</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18606,9 +19341,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>12</v>
+      </c>
+      <c r="E245" s="4">
         <v>4</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18692,9 +19430,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>12</v>
+      </c>
+      <c r="E246" s="4">
         <v>5</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18778,9 +19519,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>3</v>
+      </c>
+      <c r="E247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18864,9 +19608,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>3</v>
+      </c>
+      <c r="E248" s="4">
         <v>2</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18950,9 +19697,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>14</v>
+      </c>
+      <c r="E249" s="4">
         <v>1</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19036,9 +19786,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>14</v>
+      </c>
+      <c r="E250" s="4">
         <v>2</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19122,9 +19875,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>14</v>
+      </c>
+      <c r="E251" s="4">
         <v>3</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19208,9 +19964,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>14</v>
+      </c>
+      <c r="E252" s="4">
         <v>4</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19294,9 +20053,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>14</v>
+      </c>
+      <c r="E253" s="4">
         <v>5</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19380,9 +20142,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>7</v>
+      </c>
+      <c r="E254" s="4">
         <v>1</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19473,9 +20238,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>7</v>
+      </c>
+      <c r="E255" s="4">
         <v>2</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19566,9 +20334,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>7</v>
+      </c>
+      <c r="E256" s="4">
         <v>3</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19659,9 +20430,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>4</v>
+      </c>
+      <c r="E257" s="4">
         <v>1</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19752,9 +20526,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>4</v>
+      </c>
+      <c r="E258" s="4">
         <v>2</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19845,9 +20622,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>4</v>
+      </c>
+      <c r="E259" s="4">
         <v>3</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19940,7 +20720,10 @@
       <c r="D260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="E260" s="4">
+        <v>1</v>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20041,7 +20824,10 @@
       <c r="D261" s="4">
         <v>1</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E261" s="4">
+        <v>1</v>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20095,9 +20881,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>161</v>
+      </c>
+      <c r="E262" s="4">
         <v>1</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20158,9 +20947,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>161</v>
+      </c>
+      <c r="E263" s="4">
         <v>2</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20221,9 +21013,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>161</v>
+      </c>
+      <c r="E264" s="4">
         <v>3</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20284,9 +21079,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>161</v>
+      </c>
+      <c r="E265" s="4">
         <v>4</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20347,9 +21145,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>161</v>
+      </c>
+      <c r="E266" s="4">
         <v>5</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20410,9 +21211,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>181</v>
+      </c>
+      <c r="E267" s="4">
         <v>1</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20473,9 +21277,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>181</v>
+      </c>
+      <c r="E268" s="4">
         <v>2</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20536,9 +21343,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>181</v>
+      </c>
+      <c r="E269" s="4">
         <v>3</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20599,9 +21409,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>181</v>
+      </c>
+      <c r="E270" s="4">
         <v>4</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20662,9 +21475,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>181</v>
+      </c>
+      <c r="E271" s="4">
         <v>5</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20725,9 +21541,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>246</v>
+      </c>
+      <c r="E272" s="4">
         <v>1</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20788,9 +21607,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>246</v>
+      </c>
+      <c r="E273" s="4">
         <v>2</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20851,9 +21673,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>246</v>
+      </c>
+      <c r="E274" s="4">
         <v>3</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20914,9 +21739,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>246</v>
+      </c>
+      <c r="E275" s="4">
         <v>4</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20977,9 +21805,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>246</v>
+      </c>
+      <c r="E276" s="4">
         <v>5</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21040,9 +21871,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>93</v>
+      </c>
+      <c r="E277" s="4">
         <v>1</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21111,9 +21945,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>93</v>
+      </c>
+      <c r="E278" s="4">
         <v>2</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21182,9 +22019,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>93</v>
+      </c>
+      <c r="E279" s="4">
         <v>3</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21253,9 +22093,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>93</v>
+      </c>
+      <c r="E280" s="4">
         <v>4</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21324,9 +22167,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>93</v>
+      </c>
+      <c r="E281" s="4">
         <v>5</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21395,9 +22241,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>113</v>
+      </c>
+      <c r="E282" s="4">
         <v>1</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21466,9 +22315,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>113</v>
+      </c>
+      <c r="E283" s="4">
         <v>2</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21537,9 +22389,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>113</v>
+      </c>
+      <c r="E284" s="4">
         <v>3</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21608,9 +22463,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>113</v>
+      </c>
+      <c r="E285" s="4">
         <v>4</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21679,9 +22537,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>113</v>
+      </c>
+      <c r="E286" s="4">
         <v>5</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21750,9 +22611,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>105</v>
+      </c>
+      <c r="E287" s="4">
         <v>1</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21821,9 +22685,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>105</v>
+      </c>
+      <c r="E288" s="4">
         <v>2</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21892,9 +22759,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>105</v>
+      </c>
+      <c r="E289" s="4">
         <v>3</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21963,9 +22833,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>105</v>
+      </c>
+      <c r="E290" s="4">
         <v>4</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22034,9 +22907,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>105</v>
+      </c>
+      <c r="E291" s="4">
         <v>5</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22105,9 +22981,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>85</v>
+      </c>
+      <c r="E292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22183,9 +23062,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>85</v>
+      </c>
+      <c r="E293" s="4">
         <v>2</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22261,9 +23143,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>85</v>
+      </c>
+      <c r="E294" s="4">
         <v>3</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22339,9 +23224,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>85</v>
+      </c>
+      <c r="E295" s="4">
         <v>4</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22417,9 +23305,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>85</v>
+      </c>
+      <c r="E296" s="4">
         <v>5</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22495,9 +23386,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>73</v>
+      </c>
+      <c r="E297" s="4">
         <v>1</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22573,9 +23467,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>73</v>
+      </c>
+      <c r="E298" s="4">
         <v>2</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22651,9 +23548,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>73</v>
+      </c>
+      <c r="E299" s="4">
         <v>3</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22729,9 +23629,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>73</v>
+      </c>
+      <c r="E300" s="4">
         <v>4</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22807,9 +23710,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>73</v>
+      </c>
+      <c r="E301" s="4">
         <v>5</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22885,9 +23791,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>68</v>
+      </c>
+      <c r="E302" s="4">
         <v>1</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22963,9 +23872,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>68</v>
+      </c>
+      <c r="E303" s="4">
         <v>2</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23041,9 +23953,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>68</v>
+      </c>
+      <c r="E304" s="4">
         <v>3</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23119,9 +24034,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>68</v>
+      </c>
+      <c r="E305" s="4">
         <v>4</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23197,9 +24115,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>68</v>
+      </c>
+      <c r="E306" s="4">
         <v>5</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23275,9 +24196,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>41</v>
+      </c>
+      <c r="E307" s="4">
         <v>1</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23361,9 +24285,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>41</v>
+      </c>
+      <c r="E308" s="4">
         <v>2</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23447,9 +24374,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>41</v>
+      </c>
+      <c r="E309" s="4">
         <v>3</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23533,9 +24463,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>41</v>
+      </c>
+      <c r="E310" s="4">
         <v>4</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23619,9 +24552,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>41</v>
+      </c>
+      <c r="E311" s="4">
         <v>5</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23705,9 +24641,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>33</v>
+      </c>
+      <c r="E312" s="4">
         <v>1</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23791,9 +24730,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>33</v>
+      </c>
+      <c r="E313" s="4">
         <v>2</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23877,9 +24819,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>33</v>
+      </c>
+      <c r="E314" s="4">
         <v>3</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23963,9 +24908,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>33</v>
+      </c>
+      <c r="E315" s="4">
         <v>4</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24049,9 +24997,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>33</v>
+      </c>
+      <c r="E316" s="4">
         <v>5</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24135,9 +25086,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>32</v>
+      </c>
+      <c r="E317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24221,9 +25175,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>32</v>
+      </c>
+      <c r="E318" s="4">
         <v>2</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24307,9 +25264,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>32</v>
+      </c>
+      <c r="E319" s="4">
         <v>3</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24393,9 +25353,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>32</v>
+      </c>
+      <c r="E320" s="4">
         <v>4</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24479,9 +25442,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>32</v>
+      </c>
+      <c r="E321" s="4">
         <v>5</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24565,9 +25531,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>23</v>
+      </c>
+      <c r="E322" s="4">
         <v>1</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24658,9 +25627,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>23</v>
+      </c>
+      <c r="E323" s="4">
         <v>2</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24751,9 +25723,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>23</v>
+      </c>
+      <c r="E324" s="4">
         <v>3</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24844,9 +25819,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>23</v>
+      </c>
+      <c r="E325" s="4">
         <v>4</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24937,9 +25915,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>23</v>
+      </c>
+      <c r="E326" s="4">
         <v>5</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25030,9 +26011,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>21</v>
+      </c>
+      <c r="E327" s="4">
         <v>1</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25123,9 +26107,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>21</v>
+      </c>
+      <c r="E328" s="4">
         <v>2</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25216,9 +26203,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>21</v>
+      </c>
+      <c r="E329" s="4">
         <v>3</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25309,9 +26299,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>21</v>
+      </c>
+      <c r="E330" s="4">
         <v>4</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25402,9 +26395,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>21</v>
+      </c>
+      <c r="E331" s="4">
         <v>5</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25495,9 +26491,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>19</v>
+      </c>
+      <c r="E332" s="4">
         <v>1</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25588,9 +26587,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>19</v>
+      </c>
+      <c r="E333" s="4">
         <v>2</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25681,9 +26683,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>19</v>
+      </c>
+      <c r="E334" s="4">
         <v>3</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25774,9 +26779,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>19</v>
+      </c>
+      <c r="E335" s="4">
         <v>4</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25867,9 +26875,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>19</v>
+      </c>
+      <c r="E336" s="4">
         <v>5</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25960,9 +26971,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>17</v>
+      </c>
+      <c r="E337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26061,9 +27075,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>17</v>
+      </c>
+      <c r="E338" s="4">
         <v>2</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26162,9 +27179,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>17</v>
+      </c>
+      <c r="E339" s="4">
         <v>3</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26263,9 +27283,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>17</v>
+      </c>
+      <c r="E340" s="4">
         <v>4</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26364,9 +27387,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>17</v>
+      </c>
+      <c r="E341" s="4">
         <v>5</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26465,9 +27491,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>10</v>
+      </c>
+      <c r="E342" s="4">
         <v>1</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26566,9 +27595,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>10</v>
+      </c>
+      <c r="E343" s="4">
         <v>2</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26667,9 +27699,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>10</v>
+      </c>
+      <c r="E344" s="4">
         <v>3</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26768,9 +27803,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>10</v>
+      </c>
+      <c r="E345" s="4">
         <v>1</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26869,9 +27907,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>10</v>
+      </c>
+      <c r="E346" s="4">
         <v>2</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26970,9 +28011,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>10</v>
+      </c>
+      <c r="E347" s="4">
         <v>3</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27071,9 +28115,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>10</v>
+      </c>
+      <c r="E348" s="4">
         <v>4</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27172,9 +28219,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>10</v>
+      </c>
+      <c r="E349" s="4">
         <v>5</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27273,9 +28323,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>11</v>
+      </c>
+      <c r="E350" s="4">
         <v>1</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27381,9 +28434,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>11</v>
+      </c>
+      <c r="E351" s="4">
         <v>2</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27489,9 +28545,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>11</v>
+      </c>
+      <c r="E352" s="4">
         <v>3</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27597,9 +28656,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>11</v>
+      </c>
+      <c r="E353" s="4">
         <v>4</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27705,9 +28767,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>6</v>
+      </c>
+      <c r="E354" s="4">
         <v>1</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27813,9 +28878,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>6</v>
+      </c>
+      <c r="E355" s="4">
         <v>2</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27921,9 +28989,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>6</v>
+      </c>
+      <c r="E356" s="4">
         <v>3</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28029,9 +29100,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>6</v>
+      </c>
+      <c r="E357" s="4">
         <v>4</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28137,9 +29211,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>6</v>
+      </c>
+      <c r="E358" s="4">
         <v>5</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28245,9 +29322,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>11</v>
+      </c>
+      <c r="E359" s="4">
         <v>1</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28353,9 +29433,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>11</v>
+      </c>
+      <c r="E360" s="4">
         <v>2</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28461,9 +29544,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>11</v>
+      </c>
+      <c r="E361" s="4">
         <v>3</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28569,9 +29655,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>11</v>
+      </c>
+      <c r="E362" s="4">
         <v>4</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28677,9 +29766,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>11</v>
+      </c>
+      <c r="E363" s="4">
         <v>5</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28785,9 +29877,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>5</v>
+      </c>
+      <c r="E364" s="4">
         <v>1</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28901,9 +29996,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>5</v>
+      </c>
+      <c r="E365" s="4">
         <v>2</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29017,9 +30115,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>6</v>
+      </c>
+      <c r="E366" s="4">
         <v>1</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29133,9 +30234,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>6</v>
+      </c>
+      <c r="E367" s="4">
         <v>2</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29249,9 +30353,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>6</v>
+      </c>
+      <c r="E368" s="4">
         <v>3</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29365,9 +30472,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>6</v>
+      </c>
+      <c r="E369" s="4">
         <v>4</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29481,9 +30591,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>6</v>
+      </c>
+      <c r="E370" s="4">
         <v>5</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29597,9 +30710,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>7</v>
+      </c>
+      <c r="E371" s="4">
         <v>1</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29713,9 +30829,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>7</v>
+      </c>
+      <c r="E372" s="4">
         <v>2</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29829,9 +30948,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>7</v>
+      </c>
+      <c r="E373" s="4">
         <v>3</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29945,9 +31067,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>2</v>
+      </c>
+      <c r="E374" s="4">
         <v>1</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -29973,9 +31098,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>6</v>
+      </c>
+      <c r="E375" s="4">
         <v>1</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30096,9 +31224,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>6</v>
+      </c>
+      <c r="E376" s="4">
         <v>2</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30219,9 +31350,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>6</v>
+      </c>
+      <c r="E377" s="4">
         <v>3</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30344,7 +31478,10 @@
       <c r="D378" s="4">
         <v>1</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="E378" s="4">
+        <v>1</v>
+      </c>
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30467,7 +31604,10 @@
       <c r="D379" s="4">
         <v>1</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="E379" s="4">
+        <v>1</v>
+      </c>
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30521,9 +31661,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>63</v>
+      </c>
+      <c r="E380" s="4">
         <v>1</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30584,9 +31727,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>63</v>
+      </c>
+      <c r="E381" s="4">
         <v>2</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30647,9 +31793,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>63</v>
+      </c>
+      <c r="E382" s="4">
         <v>3</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30710,9 +31859,12 @@
         </is>
       </c>
       <c r="D383" s="4">
+        <v>63</v>
+      </c>
+      <c r="E383" s="4">
         <v>4</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30773,9 +31925,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>63</v>
+      </c>
+      <c r="E384" s="4">
         <v>5</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30836,9 +31991,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>117</v>
+      </c>
+      <c r="E385" s="4">
         <v>1</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30899,9 +32057,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>117</v>
+      </c>
+      <c r="E386" s="4">
         <v>2</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30962,9 +32123,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>117</v>
+      </c>
+      <c r="E387" s="4">
         <v>3</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31025,9 +32189,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>117</v>
+      </c>
+      <c r="E388" s="4">
         <v>4</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31088,9 +32255,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>117</v>
+      </c>
+      <c r="E389" s="4">
         <v>5</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31151,9 +32321,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>170</v>
+      </c>
+      <c r="E390" s="4">
         <v>1</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31214,9 +32387,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>170</v>
+      </c>
+      <c r="E391" s="4">
         <v>2</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31277,9 +32453,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>170</v>
+      </c>
+      <c r="E392" s="4">
         <v>3</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31340,9 +32519,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>170</v>
+      </c>
+      <c r="E393" s="4">
         <v>4</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31403,9 +32585,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>170</v>
+      </c>
+      <c r="E394" s="4">
         <v>5</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31466,9 +32651,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>46</v>
+      </c>
+      <c r="E395" s="4">
         <v>1</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31537,9 +32725,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>46</v>
+      </c>
+      <c r="E396" s="4">
         <v>2</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31608,9 +32799,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>46</v>
+      </c>
+      <c r="E397" s="4">
         <v>3</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31679,9 +32873,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>46</v>
+      </c>
+      <c r="E398" s="4">
         <v>4</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31750,9 +32947,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>46</v>
+      </c>
+      <c r="E399" s="4">
         <v>5</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31821,9 +33021,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>103</v>
+      </c>
+      <c r="E400" s="4">
         <v>1</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31892,9 +33095,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>103</v>
+      </c>
+      <c r="E401" s="4">
         <v>2</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31963,9 +33169,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>103</v>
+      </c>
+      <c r="E402" s="4">
         <v>3</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32034,9 +33243,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>103</v>
+      </c>
+      <c r="E403" s="4">
         <v>4</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32105,9 +33317,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>103</v>
+      </c>
+      <c r="E404" s="4">
         <v>5</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32176,9 +33391,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>103</v>
+      </c>
+      <c r="E405" s="4">
         <v>1</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32247,9 +33465,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>103</v>
+      </c>
+      <c r="E406" s="4">
         <v>2</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32318,9 +33539,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>103</v>
+      </c>
+      <c r="E407" s="4">
         <v>3</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32389,9 +33613,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>103</v>
+      </c>
+      <c r="E408" s="4">
         <v>4</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32460,9 +33687,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>103</v>
+      </c>
+      <c r="E409" s="4">
         <v>5</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32531,9 +33761,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>51</v>
+      </c>
+      <c r="E410" s="4">
         <v>1</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32609,9 +33842,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>51</v>
+      </c>
+      <c r="E411" s="4">
         <v>2</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32687,9 +33923,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>51</v>
+      </c>
+      <c r="E412" s="4">
         <v>3</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32765,9 +34004,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>51</v>
+      </c>
+      <c r="E413" s="4">
         <v>4</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32843,9 +34085,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>51</v>
+      </c>
+      <c r="E414" s="4">
         <v>5</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32921,9 +34166,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>62</v>
+      </c>
+      <c r="E415" s="4">
         <v>1</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32999,9 +34247,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>62</v>
+      </c>
+      <c r="E416" s="4">
         <v>2</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33077,9 +34328,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>62</v>
+      </c>
+      <c r="E417" s="4">
         <v>3</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33155,9 +34409,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>62</v>
+      </c>
+      <c r="E418" s="4">
         <v>4</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33233,9 +34490,12 @@
         </is>
       </c>
       <c r="D419" s="4">
+        <v>62</v>
+      </c>
+      <c r="E419" s="4">
         <v>5</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33311,9 +34571,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>44</v>
+      </c>
+      <c r="E420" s="4">
         <v>1</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33389,9 +34652,12 @@
         </is>
       </c>
       <c r="D421" s="4">
+        <v>44</v>
+      </c>
+      <c r="E421" s="4">
         <v>2</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33467,9 +34733,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>44</v>
+      </c>
+      <c r="E422" s="4">
         <v>3</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33545,9 +34814,12 @@
         </is>
       </c>
       <c r="D423" s="4">
+        <v>44</v>
+      </c>
+      <c r="E423" s="4">
         <v>4</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33623,9 +34895,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>44</v>
+      </c>
+      <c r="E424" s="4">
         <v>5</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33701,9 +34976,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>23</v>
+      </c>
+      <c r="E425" s="4">
         <v>1</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33787,9 +35065,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>23</v>
+      </c>
+      <c r="E426" s="4">
         <v>2</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33873,9 +35154,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>23</v>
+      </c>
+      <c r="E427" s="4">
         <v>3</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33959,9 +35243,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>23</v>
+      </c>
+      <c r="E428" s="4">
         <v>4</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34045,9 +35332,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>23</v>
+      </c>
+      <c r="E429" s="4">
         <v>5</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34131,9 +35421,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>33</v>
+      </c>
+      <c r="E430" s="4">
         <v>1</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34217,9 +35510,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>33</v>
+      </c>
+      <c r="E431" s="4">
         <v>2</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34303,9 +35599,12 @@
         </is>
       </c>
       <c r="D432" s="4">
+        <v>33</v>
+      </c>
+      <c r="E432" s="4">
         <v>3</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34389,9 +35688,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>33</v>
+      </c>
+      <c r="E433" s="4">
         <v>4</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34475,9 +35777,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>33</v>
+      </c>
+      <c r="E434" s="4">
         <v>5</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34561,9 +35866,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>26</v>
+      </c>
+      <c r="E435" s="4">
         <v>1</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34647,9 +35955,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>26</v>
+      </c>
+      <c r="E436" s="4">
         <v>2</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34733,9 +36044,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>26</v>
+      </c>
+      <c r="E437" s="4">
         <v>3</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34819,9 +36133,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>26</v>
+      </c>
+      <c r="E438" s="4">
         <v>4</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34905,9 +36222,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>26</v>
+      </c>
+      <c r="E439" s="4">
         <v>5</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34991,9 +36311,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>10</v>
+      </c>
+      <c r="E440" s="4">
         <v>1</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35084,9 +36407,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>10</v>
+      </c>
+      <c r="E441" s="4">
         <v>2</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35177,9 +36503,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>10</v>
+      </c>
+      <c r="E442" s="4">
         <v>3</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35270,9 +36599,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>8</v>
+      </c>
+      <c r="E443" s="4">
         <v>1</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35363,9 +36695,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>8</v>
+      </c>
+      <c r="E444" s="4">
         <v>2</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35456,9 +36791,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>8</v>
+      </c>
+      <c r="E445" s="4">
         <v>3</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35549,9 +36887,12 @@
         </is>
       </c>
       <c r="D446" s="4">
+        <v>8</v>
+      </c>
+      <c r="E446" s="4">
         <v>4</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35642,9 +36983,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>10</v>
+      </c>
+      <c r="E447" s="4">
         <v>1</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35735,9 +37079,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>10</v>
+      </c>
+      <c r="E448" s="4">
         <v>2</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35828,9 +37175,12 @@
         </is>
       </c>
       <c r="D449" s="4">
+        <v>10</v>
+      </c>
+      <c r="E449" s="4">
         <v>3</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35921,9 +37271,12 @@
         </is>
       </c>
       <c r="D450" s="4">
+        <v>10</v>
+      </c>
+      <c r="E450" s="4">
         <v>4</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36014,9 +37367,12 @@
         </is>
       </c>
       <c r="D451" s="4">
+        <v>10</v>
+      </c>
+      <c r="E451" s="4">
         <v>5</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36107,9 +37463,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>8</v>
+      </c>
+      <c r="E452" s="4">
         <v>1</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36208,9 +37567,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>8</v>
+      </c>
+      <c r="E453" s="4">
         <v>2</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36309,9 +37671,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>13</v>
+      </c>
+      <c r="E454" s="4">
         <v>1</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36410,9 +37775,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>13</v>
+      </c>
+      <c r="E455" s="4">
         <v>2</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36511,9 +37879,12 @@
         </is>
       </c>
       <c r="D456" s="4">
+        <v>13</v>
+      </c>
+      <c r="E456" s="4">
         <v>3</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36612,9 +37983,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>13</v>
+      </c>
+      <c r="E457" s="4">
         <v>4</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36713,9 +38087,12 @@
         </is>
       </c>
       <c r="D458" s="4">
+        <v>10</v>
+      </c>
+      <c r="E458" s="4">
         <v>1</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36814,9 +38191,12 @@
         </is>
       </c>
       <c r="D459" s="4">
+        <v>10</v>
+      </c>
+      <c r="E459" s="4">
         <v>2</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36915,9 +38295,12 @@
         </is>
       </c>
       <c r="D460" s="4">
+        <v>10</v>
+      </c>
+      <c r="E460" s="4">
         <v>3</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37016,9 +38399,12 @@
         </is>
       </c>
       <c r="D461" s="4">
+        <v>10</v>
+      </c>
+      <c r="E461" s="4">
         <v>4</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37117,9 +38503,12 @@
         </is>
       </c>
       <c r="D462" s="4">
+        <v>5</v>
+      </c>
+      <c r="E462" s="4">
         <v>1</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37225,9 +38614,12 @@
         </is>
       </c>
       <c r="D463" s="4">
+        <v>7</v>
+      </c>
+      <c r="E463" s="4">
         <v>1</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37333,9 +38725,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>7</v>
+      </c>
+      <c r="E464" s="4">
         <v>2</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37441,9 +38836,12 @@
         </is>
       </c>
       <c r="D465" s="4">
+        <v>7</v>
+      </c>
+      <c r="E465" s="4">
         <v>3</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37549,9 +38947,12 @@
         </is>
       </c>
       <c r="D466" s="4">
+        <v>7</v>
+      </c>
+      <c r="E466" s="4">
         <v>4</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37657,9 +39058,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>5</v>
+      </c>
+      <c r="E467" s="4">
         <v>1</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37765,9 +39169,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>5</v>
+      </c>
+      <c r="E468" s="4">
         <v>2</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37875,7 +39282,10 @@
       <c r="D469" s="4">
         <v>1</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="E469" s="4">
+        <v>1</v>
+      </c>
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37989,9 +39399,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>4</v>
+      </c>
+      <c r="E470" s="4">
         <v>1</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38105,9 +39518,12 @@
         </is>
       </c>
       <c r="D471" s="4">
+        <v>2</v>
+      </c>
+      <c r="E471" s="4">
         <v>1</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38228,9 +39644,12 @@
         </is>
       </c>
       <c r="D472" s="4">
+        <v>4</v>
+      </c>
+      <c r="E472" s="4">
         <v>1</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38351,9 +39770,12 @@
         </is>
       </c>
       <c r="D473" s="4">
+        <v>4</v>
+      </c>
+      <c r="E473" s="4">
         <v>2</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38476,7 +39898,10 @@
       <c r="D474" s="4">
         <v>1</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="E474" s="4">
+        <v>1</v>
+      </c>
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -38502,9 +39927,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>78</v>
+      </c>
+      <c r="E475" s="4">
         <v>1</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38565,9 +39993,12 @@
         </is>
       </c>
       <c r="D476" s="4">
+        <v>78</v>
+      </c>
+      <c r="E476" s="4">
         <v>2</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38628,9 +40059,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>78</v>
+      </c>
+      <c r="E477" s="4">
         <v>3</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38691,9 +40125,12 @@
         </is>
       </c>
       <c r="D478" s="4">
+        <v>78</v>
+      </c>
+      <c r="E478" s="4">
         <v>4</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38754,9 +40191,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>78</v>
+      </c>
+      <c r="E479" s="4">
         <v>5</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38817,9 +40257,12 @@
         </is>
       </c>
       <c r="D480" s="4">
+        <v>143</v>
+      </c>
+      <c r="E480" s="4">
         <v>1</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38880,9 +40323,12 @@
         </is>
       </c>
       <c r="D481" s="4">
+        <v>143</v>
+      </c>
+      <c r="E481" s="4">
         <v>2</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38943,9 +40389,12 @@
         </is>
       </c>
       <c r="D482" s="4">
+        <v>143</v>
+      </c>
+      <c r="E482" s="4">
         <v>3</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39006,9 +40455,12 @@
         </is>
       </c>
       <c r="D483" s="4">
+        <v>143</v>
+      </c>
+      <c r="E483" s="4">
         <v>4</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39069,9 +40521,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>143</v>
+      </c>
+      <c r="E484" s="4">
         <v>5</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39132,9 +40587,12 @@
         </is>
       </c>
       <c r="D485" s="4">
+        <v>121</v>
+      </c>
+      <c r="E485" s="4">
         <v>1</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39195,9 +40653,12 @@
         </is>
       </c>
       <c r="D486" s="4">
+        <v>121</v>
+      </c>
+      <c r="E486" s="4">
         <v>2</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39258,9 +40719,12 @@
         </is>
       </c>
       <c r="D487" s="4">
+        <v>121</v>
+      </c>
+      <c r="E487" s="4">
         <v>3</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39321,9 +40785,12 @@
         </is>
       </c>
       <c r="D488" s="4">
+        <v>121</v>
+      </c>
+      <c r="E488" s="4">
         <v>4</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39384,9 +40851,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>121</v>
+      </c>
+      <c r="E489" s="4">
         <v>5</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39447,9 +40917,12 @@
         </is>
       </c>
       <c r="D490" s="4">
+        <v>66</v>
+      </c>
+      <c r="E490" s="4">
         <v>1</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39518,9 +40991,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>66</v>
+      </c>
+      <c r="E491" s="4">
         <v>2</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39589,9 +41065,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>66</v>
+      </c>
+      <c r="E492" s="4">
         <v>3</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39660,9 +41139,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>66</v>
+      </c>
+      <c r="E493" s="4">
         <v>4</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39731,9 +41213,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>66</v>
+      </c>
+      <c r="E494" s="4">
         <v>5</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39802,9 +41287,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>76</v>
+      </c>
+      <c r="E495" s="4">
         <v>1</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39873,9 +41361,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>76</v>
+      </c>
+      <c r="E496" s="4">
         <v>2</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39944,9 +41435,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>76</v>
+      </c>
+      <c r="E497" s="4">
         <v>3</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40015,9 +41509,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>76</v>
+      </c>
+      <c r="E498" s="4">
         <v>4</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40086,9 +41583,12 @@
         </is>
       </c>
       <c r="D499" s="4">
+        <v>76</v>
+      </c>
+      <c r="E499" s="4">
         <v>5</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40157,9 +41657,12 @@
         </is>
       </c>
       <c r="D500" s="4">
+        <v>77</v>
+      </c>
+      <c r="E500" s="4">
         <v>1</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40228,9 +41731,12 @@
         </is>
       </c>
       <c r="D501" s="4">
+        <v>77</v>
+      </c>
+      <c r="E501" s="4">
         <v>2</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40299,9 +41805,12 @@
         </is>
       </c>
       <c r="D502" s="4">
+        <v>77</v>
+      </c>
+      <c r="E502" s="4">
         <v>3</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40370,9 +41879,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>77</v>
+      </c>
+      <c r="E503" s="4">
         <v>4</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40441,9 +41953,12 @@
         </is>
       </c>
       <c r="D504" s="4">
+        <v>77</v>
+      </c>
+      <c r="E504" s="4">
         <v>5</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40512,9 +42027,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>41</v>
+      </c>
+      <c r="E505" s="4">
         <v>1</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40590,9 +42108,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>41</v>
+      </c>
+      <c r="E506" s="4">
         <v>2</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40668,9 +42189,12 @@
         </is>
       </c>
       <c r="D507" s="4">
+        <v>41</v>
+      </c>
+      <c r="E507" s="4">
         <v>3</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40746,9 +42270,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>41</v>
+      </c>
+      <c r="E508" s="4">
         <v>4</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40824,9 +42351,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>41</v>
+      </c>
+      <c r="E509" s="4">
         <v>5</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40902,9 +42432,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>27</v>
+      </c>
+      <c r="E510" s="4">
         <v>1</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40980,9 +42513,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>27</v>
+      </c>
+      <c r="E511" s="4">
         <v>2</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41058,9 +42594,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>27</v>
+      </c>
+      <c r="E512" s="4">
         <v>3</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41136,9 +42675,12 @@
         </is>
       </c>
       <c r="D513" s="4">
+        <v>27</v>
+      </c>
+      <c r="E513" s="4">
         <v>4</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41214,9 +42756,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>27</v>
+      </c>
+      <c r="E514" s="4">
         <v>5</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41292,9 +42837,12 @@
         </is>
       </c>
       <c r="D515" s="4">
+        <v>54</v>
+      </c>
+      <c r="E515" s="4">
         <v>1</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41370,9 +42918,12 @@
         </is>
       </c>
       <c r="D516" s="4">
+        <v>54</v>
+      </c>
+      <c r="E516" s="4">
         <v>2</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41448,9 +42999,12 @@
         </is>
       </c>
       <c r="D517" s="4">
+        <v>54</v>
+      </c>
+      <c r="E517" s="4">
         <v>3</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41526,9 +43080,12 @@
         </is>
       </c>
       <c r="D518" s="4">
+        <v>54</v>
+      </c>
+      <c r="E518" s="4">
         <v>4</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41604,9 +43161,12 @@
         </is>
       </c>
       <c r="D519" s="4">
+        <v>54</v>
+      </c>
+      <c r="E519" s="4">
         <v>5</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41682,9 +43242,12 @@
         </is>
       </c>
       <c r="D520" s="4">
+        <v>25</v>
+      </c>
+      <c r="E520" s="4">
         <v>1</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41768,9 +43331,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>25</v>
+      </c>
+      <c r="E521" s="4">
         <v>2</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41854,9 +43420,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>25</v>
+      </c>
+      <c r="E522" s="4">
         <v>3</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41940,9 +43509,12 @@
         </is>
       </c>
       <c r="D523" s="4">
+        <v>25</v>
+      </c>
+      <c r="E523" s="4">
         <v>4</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42026,9 +43598,12 @@
         </is>
       </c>
       <c r="D524" s="4">
+        <v>25</v>
+      </c>
+      <c r="E524" s="4">
         <v>5</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42112,9 +43687,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>30</v>
+      </c>
+      <c r="E525" s="4">
         <v>1</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42198,9 +43776,12 @@
         </is>
       </c>
       <c r="D526" s="4">
+        <v>30</v>
+      </c>
+      <c r="E526" s="4">
         <v>2</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42284,9 +43865,12 @@
         </is>
       </c>
       <c r="D527" s="4">
+        <v>30</v>
+      </c>
+      <c r="E527" s="4">
         <v>3</v>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42370,9 +43954,12 @@
         </is>
       </c>
       <c r="D528" s="4">
+        <v>30</v>
+      </c>
+      <c r="E528" s="4">
         <v>4</v>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="F528" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42456,9 +44043,12 @@
         </is>
       </c>
       <c r="D529" s="4">
+        <v>30</v>
+      </c>
+      <c r="E529" s="4">
         <v>5</v>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="F529" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42542,9 +44132,12 @@
         </is>
       </c>
       <c r="D530" s="4">
+        <v>13</v>
+      </c>
+      <c r="E530" s="4">
         <v>1</v>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="F530" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42628,9 +44221,12 @@
         </is>
       </c>
       <c r="D531" s="4">
+        <v>13</v>
+      </c>
+      <c r="E531" s="4">
         <v>2</v>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="F531" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42714,9 +44310,12 @@
         </is>
       </c>
       <c r="D532" s="4">
+        <v>13</v>
+      </c>
+      <c r="E532" s="4">
         <v>3</v>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="F532" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42800,9 +44399,12 @@
         </is>
       </c>
       <c r="D533" s="4">
+        <v>13</v>
+      </c>
+      <c r="E533" s="4">
         <v>4</v>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42886,9 +44488,12 @@
         </is>
       </c>
       <c r="D534" s="4">
+        <v>13</v>
+      </c>
+      <c r="E534" s="4">
         <v>5</v>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42972,9 +44577,12 @@
         </is>
       </c>
       <c r="D535" s="4">
+        <v>14</v>
+      </c>
+      <c r="E535" s="4">
         <v>1</v>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="F535" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43065,9 +44673,12 @@
         </is>
       </c>
       <c r="D536" s="4">
+        <v>14</v>
+      </c>
+      <c r="E536" s="4">
         <v>2</v>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="F536" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43158,9 +44769,12 @@
         </is>
       </c>
       <c r="D537" s="4">
+        <v>14</v>
+      </c>
+      <c r="E537" s="4">
         <v>3</v>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="F537" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43251,9 +44865,12 @@
         </is>
       </c>
       <c r="D538" s="4">
+        <v>14</v>
+      </c>
+      <c r="E538" s="4">
         <v>4</v>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="F538" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43344,9 +44961,12 @@
         </is>
       </c>
       <c r="D539" s="4">
+        <v>14</v>
+      </c>
+      <c r="E539" s="4">
         <v>5</v>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="F539" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43437,9 +45057,12 @@
         </is>
       </c>
       <c r="D540" s="4">
+        <v>8</v>
+      </c>
+      <c r="E540" s="4">
         <v>1</v>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="F540" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43530,9 +45153,12 @@
         </is>
       </c>
       <c r="D541" s="4">
+        <v>8</v>
+      </c>
+      <c r="E541" s="4">
         <v>2</v>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43623,9 +45249,12 @@
         </is>
       </c>
       <c r="D542" s="4">
+        <v>8</v>
+      </c>
+      <c r="E542" s="4">
         <v>3</v>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="F542" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43716,9 +45345,12 @@
         </is>
       </c>
       <c r="D543" s="4">
+        <v>9</v>
+      </c>
+      <c r="E543" s="4">
         <v>1</v>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="F543" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43809,9 +45441,12 @@
         </is>
       </c>
       <c r="D544" s="4">
+        <v>9</v>
+      </c>
+      <c r="E544" s="4">
         <v>2</v>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="F544" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43902,9 +45537,12 @@
         </is>
       </c>
       <c r="D545" s="4">
+        <v>9</v>
+      </c>
+      <c r="E545" s="4">
         <v>3</v>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="F545" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43995,9 +45633,12 @@
         </is>
       </c>
       <c r="D546" s="4">
+        <v>9</v>
+      </c>
+      <c r="E546" s="4">
         <v>4</v>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="F546" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44088,9 +45729,12 @@
         </is>
       </c>
       <c r="D547" s="4">
+        <v>9</v>
+      </c>
+      <c r="E547" s="4">
         <v>5</v>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="F547" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44181,9 +45825,12 @@
         </is>
       </c>
       <c r="D548" s="4">
+        <v>4</v>
+      </c>
+      <c r="E548" s="4">
         <v>1</v>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="F548" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44282,9 +45929,12 @@
         </is>
       </c>
       <c r="D549" s="4">
+        <v>4</v>
+      </c>
+      <c r="E549" s="4">
         <v>1</v>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="F549" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44383,9 +46033,12 @@
         </is>
       </c>
       <c r="D550" s="4">
+        <v>4</v>
+      </c>
+      <c r="E550" s="4">
         <v>1</v>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="F550" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44484,9 +46137,12 @@
         </is>
       </c>
       <c r="D551" s="4">
+        <v>3</v>
+      </c>
+      <c r="E551" s="4">
         <v>1</v>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="F551" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -44512,9 +46168,12 @@
         </is>
       </c>
       <c r="D552" s="4">
+        <v>2</v>
+      </c>
+      <c r="E552" s="4">
         <v>1</v>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44620,9 +46279,12 @@
         </is>
       </c>
       <c r="D553" s="4">
+        <v>6</v>
+      </c>
+      <c r="E553" s="4">
         <v>1</v>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="F553" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44728,9 +46390,12 @@
         </is>
       </c>
       <c r="D554" s="4">
+        <v>6</v>
+      </c>
+      <c r="E554" s="4">
         <v>2</v>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="F554" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44836,9 +46501,12 @@
         </is>
       </c>
       <c r="D555" s="4">
+        <v>6</v>
+      </c>
+      <c r="E555" s="4">
         <v>3</v>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="F555" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44946,7 +46614,10 @@
       <c r="D556" s="4">
         <v>1</v>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="E556" s="4">
+        <v>1</v>
+      </c>
+      <c r="F556" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45060,9 +46731,12 @@
         </is>
       </c>
       <c r="D557" s="4">
+        <v>2</v>
+      </c>
+      <c r="E557" s="4">
         <v>1</v>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="F557" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -45088,9 +46762,12 @@
         </is>
       </c>
       <c r="D558" s="4">
+        <v>4</v>
+      </c>
+      <c r="E558" s="4">
         <v>1</v>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="F558" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45211,9 +46888,12 @@
         </is>
       </c>
       <c r="D559" s="4">
+        <v>4</v>
+      </c>
+      <c r="E559" s="4">
         <v>2</v>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45336,7 +47016,10 @@
       <c r="D560" s="4">
         <v>1</v>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="E560" s="4">
+        <v>1</v>
+      </c>
+      <c r="F560" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45392,7 +47075,10 @@
       <c r="D561" s="4">
         <v>1</v>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="E561" s="4">
+        <v>1</v>
+      </c>
+      <c r="F561" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45448,7 +47134,10 @@
       <c r="D562" s="4">
         <v>1</v>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="E562" s="4">
+        <v>1</v>
+      </c>
+      <c r="F562" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45502,9 +47191,12 @@
         </is>
       </c>
       <c r="D563" s="4">
+        <v>2</v>
+      </c>
+      <c r="E563" s="4">
         <v>1</v>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="F563" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45560,7 +47252,10 @@
       <c r="D564" s="4">
         <v>2</v>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="E564" s="4">
+        <v>2</v>
+      </c>
+      <c r="F564" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45614,9 +47309,12 @@
         </is>
       </c>
       <c r="D565" s="4">
+        <v>2</v>
+      </c>
+      <c r="E565" s="4">
         <v>1</v>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="F565" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45672,7 +47370,10 @@
       <c r="D566" s="4">
         <v>2</v>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="E566" s="4">
+        <v>2</v>
+      </c>
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45728,7 +47429,10 @@
       <c r="D567" s="4">
         <v>1</v>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="E567" s="4">
+        <v>1</v>
+      </c>
+      <c r="F567" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45800,7 +47504,10 @@
       <c r="D568" s="4">
         <v>1</v>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="E568" s="4">
+        <v>1</v>
+      </c>
+      <c r="F568" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45861,9 +47568,12 @@
         </is>
       </c>
       <c r="D569" s="4">
+        <v>7</v>
+      </c>
+      <c r="E569" s="4">
         <v>1</v>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="F569" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45924,9 +47634,12 @@
         </is>
       </c>
       <c r="D570" s="4">
+        <v>7</v>
+      </c>
+      <c r="E570" s="4">
         <v>2</v>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="F570" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45987,9 +47700,12 @@
         </is>
       </c>
       <c r="D571" s="4">
+        <v>7</v>
+      </c>
+      <c r="E571" s="4">
         <v>3</v>
       </c>
-      <c r="E571" s="6" t="inlineStr">
+      <c r="F571" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46050,9 +47766,12 @@
         </is>
       </c>
       <c r="D572" s="4">
+        <v>7</v>
+      </c>
+      <c r="E572" s="4">
         <v>4</v>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="F572" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46113,9 +47832,12 @@
         </is>
       </c>
       <c r="D573" s="4">
+        <v>7</v>
+      </c>
+      <c r="E573" s="4">
         <v>5</v>
       </c>
-      <c r="E573" s="6" t="inlineStr">
+      <c r="F573" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46176,9 +47898,12 @@
         </is>
       </c>
       <c r="D574" s="4">
+        <v>7</v>
+      </c>
+      <c r="E574" s="4">
         <v>6</v>
       </c>
-      <c r="E574" s="6" t="inlineStr">
+      <c r="F574" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46241,7 +47966,10 @@
       <c r="D575" s="4">
         <v>7</v>
       </c>
-      <c r="E575" s="6" t="inlineStr">
+      <c r="E575" s="4">
+        <v>7</v>
+      </c>
+      <c r="F575" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46304,7 +48032,10 @@
       <c r="D576" s="4">
         <v>1</v>
       </c>
-      <c r="E576" s="6" t="inlineStr">
+      <c r="E576" s="4">
+        <v>1</v>
+      </c>
+      <c r="F576" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46375,7 +48106,10 @@
       <c r="D577" s="4">
         <v>1</v>
       </c>
-      <c r="E577" s="6" t="inlineStr">
+      <c r="E577" s="4">
+        <v>1</v>
+      </c>
+      <c r="F577" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46445,9 +48179,12 @@
         </is>
       </c>
       <c r="D578" s="4">
+        <v>3</v>
+      </c>
+      <c r="E578" s="4">
         <v>1</v>
       </c>
-      <c r="E578" s="6" t="inlineStr">
+      <c r="F578" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46508,9 +48245,12 @@
         </is>
       </c>
       <c r="D579" s="4">
+        <v>3</v>
+      </c>
+      <c r="E579" s="4">
         <v>2</v>
       </c>
-      <c r="E579" s="6" t="inlineStr">
+      <c r="F579" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46573,7 +48313,10 @@
       <c r="D580" s="4">
         <v>3</v>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="E580" s="4">
+        <v>3</v>
+      </c>
+      <c r="F580" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46636,7 +48379,10 @@
       <c r="D581" s="4">
         <v>1</v>
       </c>
-      <c r="E581" s="6" t="inlineStr">
+      <c r="E581" s="4">
+        <v>1</v>
+      </c>
+      <c r="F581" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46707,7 +48453,10 @@
       <c r="D582" s="4">
         <v>1</v>
       </c>
-      <c r="E582" s="6" t="inlineStr">
+      <c r="E582" s="4">
+        <v>1</v>
+      </c>
+      <c r="F582" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46783,9 +48532,12 @@
         </is>
       </c>
       <c r="D583" s="4">
+        <v>2</v>
+      </c>
+      <c r="E583" s="4">
         <v>1</v>
       </c>
-      <c r="E583" s="6" t="inlineStr">
+      <c r="F583" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46848,7 +48600,10 @@
       <c r="D584" s="4">
         <v>2</v>
       </c>
-      <c r="E584" s="6" t="inlineStr">
+      <c r="E584" s="4">
+        <v>2</v>
+      </c>
+      <c r="F584" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46911,7 +48666,10 @@
       <c r="D585" s="4">
         <v>1</v>
       </c>
-      <c r="E585" s="6" t="inlineStr">
+      <c r="E585" s="4">
+        <v>1</v>
+      </c>
+      <c r="F585" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46972,9 +48730,12 @@
         </is>
       </c>
       <c r="D586" s="4">
+        <v>3</v>
+      </c>
+      <c r="E586" s="4">
         <v>1</v>
       </c>
-      <c r="E586" s="6" t="inlineStr">
+      <c r="F586" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47035,9 +48796,12 @@
         </is>
       </c>
       <c r="D587" s="4">
+        <v>3</v>
+      </c>
+      <c r="E587" s="4">
         <v>2</v>
       </c>
-      <c r="E587" s="6" t="inlineStr">
+      <c r="F587" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47098,9 +48862,12 @@
         </is>
       </c>
       <c r="D588" s="4">
+        <v>2</v>
+      </c>
+      <c r="E588" s="4">
         <v>1</v>
       </c>
-      <c r="E588" s="6" t="inlineStr">
+      <c r="F588" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47172,7 +48939,10 @@
       <c r="D589" s="4">
         <v>2</v>
       </c>
-      <c r="E589" s="6" t="inlineStr">
+      <c r="E589" s="4">
+        <v>2</v>
+      </c>
+      <c r="F589" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47242,9 +49012,12 @@
         </is>
       </c>
       <c r="D590" s="4">
+        <v>3</v>
+      </c>
+      <c r="E590" s="4">
         <v>1</v>
       </c>
-      <c r="E590" s="6" t="inlineStr">
+      <c r="F590" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47314,9 +49087,12 @@
         </is>
       </c>
       <c r="D591" s="4">
+        <v>3</v>
+      </c>
+      <c r="E591" s="4">
         <v>2</v>
       </c>
-      <c r="E591" s="6" t="inlineStr">
+      <c r="F591" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47388,7 +49164,10 @@
       <c r="D592" s="4">
         <v>3</v>
       </c>
-      <c r="E592" s="6" t="inlineStr">
+      <c r="E592" s="4">
+        <v>3</v>
+      </c>
+      <c r="F592" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47460,7 +49239,10 @@
       <c r="D593" s="4">
         <v>1</v>
       </c>
-      <c r="E593" s="6" t="inlineStr">
+      <c r="E593" s="4">
+        <v>1</v>
+      </c>
+      <c r="F593" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47514,9 +49296,12 @@
         </is>
       </c>
       <c r="D594" s="4">
+        <v>3</v>
+      </c>
+      <c r="E594" s="4">
         <v>1</v>
       </c>
-      <c r="E594" s="6" t="inlineStr">
+      <c r="F594" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47592,9 +49377,12 @@
         </is>
       </c>
       <c r="D595" s="4">
+        <v>3</v>
+      </c>
+      <c r="E595" s="4">
         <v>2</v>
       </c>
-      <c r="E595" s="6" t="inlineStr">
+      <c r="F595" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47665,7 +49453,10 @@
       <c r="D596" s="4">
         <v>3</v>
       </c>
-      <c r="E596" s="6" t="inlineStr">
+      <c r="E596" s="4">
+        <v>3</v>
+      </c>
+      <c r="F596" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47741,9 +49532,12 @@
         </is>
       </c>
       <c r="D597" s="4">
+        <v>3</v>
+      </c>
+      <c r="E597" s="4">
         <v>1</v>
       </c>
-      <c r="E597" s="6" t="inlineStr">
+      <c r="F597" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47827,9 +49621,12 @@
         </is>
       </c>
       <c r="D598" s="4">
+        <v>3</v>
+      </c>
+      <c r="E598" s="4">
         <v>2</v>
       </c>
-      <c r="E598" s="6" t="inlineStr">
+      <c r="F598" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47915,7 +49712,10 @@
       <c r="D599" s="4">
         <v>3</v>
       </c>
-      <c r="E599" s="6" t="inlineStr">
+      <c r="E599" s="4">
+        <v>3</v>
+      </c>
+      <c r="F599" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -47999,9 +49799,12 @@
         </is>
       </c>
       <c r="D600" s="4">
+        <v>5</v>
+      </c>
+      <c r="E600" s="4">
         <v>1</v>
       </c>
-      <c r="E600" s="6" t="inlineStr">
+      <c r="F600" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48092,9 +49895,12 @@
         </is>
       </c>
       <c r="D601" s="4">
+        <v>5</v>
+      </c>
+      <c r="E601" s="4">
         <v>2</v>
       </c>
-      <c r="E601" s="6" t="inlineStr">
+      <c r="F601" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48185,9 +49991,12 @@
         </is>
       </c>
       <c r="D602" s="4">
+        <v>5</v>
+      </c>
+      <c r="E602" s="4">
         <v>3</v>
       </c>
-      <c r="E602" s="6" t="inlineStr">
+      <c r="F602" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48286,9 +50095,12 @@
         </is>
       </c>
       <c r="D603" s="4">
+        <v>5</v>
+      </c>
+      <c r="E603" s="4">
         <v>4</v>
       </c>
-      <c r="E603" s="6" t="inlineStr">
+      <c r="F603" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48396,7 +50208,10 @@
       <c r="D604" s="4">
         <v>5</v>
       </c>
-      <c r="E604" s="6" t="inlineStr">
+      <c r="E604" s="4">
+        <v>5</v>
+      </c>
+      <c r="F604" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48489,7 +50304,10 @@
       <c r="D605" s="4">
         <v>1</v>
       </c>
-      <c r="E605" s="6" t="inlineStr">
+      <c r="E605" s="4">
+        <v>1</v>
+      </c>
+      <c r="F605" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48552,7 +50370,10 @@
       <c r="D606" s="4">
         <v>1</v>
       </c>
-      <c r="E606" s="6" t="inlineStr">
+      <c r="E606" s="4">
+        <v>1</v>
+      </c>
+      <c r="F606" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48623,7 +50444,10 @@
       <c r="D607" s="4">
         <v>1</v>
       </c>
-      <c r="E607" s="6" t="inlineStr">
+      <c r="E607" s="4">
+        <v>1</v>
+      </c>
+      <c r="F607" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48722,9 +50546,12 @@
         </is>
       </c>
       <c r="D608" s="4">
+        <v>2</v>
+      </c>
+      <c r="E608" s="4">
         <v>1</v>
       </c>
-      <c r="E608" s="6" t="inlineStr">
+      <c r="F608" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48787,7 +50614,10 @@
       <c r="D609" s="4">
         <v>2</v>
       </c>
-      <c r="E609" s="6" t="inlineStr">
+      <c r="E609" s="4">
+        <v>2</v>
+      </c>
+      <c r="F609" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48848,9 +50678,12 @@
         </is>
       </c>
       <c r="D610" s="4">
+        <v>7</v>
+      </c>
+      <c r="E610" s="4">
         <v>1</v>
       </c>
-      <c r="E610" s="6" t="inlineStr">
+      <c r="F610" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48911,9 +50744,12 @@
         </is>
       </c>
       <c r="D611" s="4">
+        <v>7</v>
+      </c>
+      <c r="E611" s="4">
         <v>2</v>
       </c>
-      <c r="E611" s="6" t="inlineStr">
+      <c r="F611" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -48974,9 +50810,12 @@
         </is>
       </c>
       <c r="D612" s="4">
+        <v>7</v>
+      </c>
+      <c r="E612" s="4">
         <v>3</v>
       </c>
-      <c r="E612" s="6" t="inlineStr">
+      <c r="F612" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49037,9 +50876,12 @@
         </is>
       </c>
       <c r="D613" s="4">
+        <v>7</v>
+      </c>
+      <c r="E613" s="4">
         <v>4</v>
       </c>
-      <c r="E613" s="6" t="inlineStr">
+      <c r="F613" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49100,9 +50942,12 @@
         </is>
       </c>
       <c r="D614" s="4">
+        <v>7</v>
+      </c>
+      <c r="E614" s="4">
         <v>5</v>
       </c>
-      <c r="E614" s="6" t="inlineStr">
+      <c r="F614" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49163,9 +51008,12 @@
         </is>
       </c>
       <c r="D615" s="4">
+        <v>7</v>
+      </c>
+      <c r="E615" s="4">
         <v>6</v>
       </c>
-      <c r="E615" s="6" t="inlineStr">
+      <c r="F615" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49228,7 +51076,10 @@
       <c r="D616" s="4">
         <v>7</v>
       </c>
-      <c r="E616" s="6" t="inlineStr">
+      <c r="E616" s="4">
+        <v>7</v>
+      </c>
+      <c r="F616" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49289,9 +51140,12 @@
         </is>
       </c>
       <c r="D617" s="4">
+        <v>2</v>
+      </c>
+      <c r="E617" s="4">
         <v>1</v>
       </c>
-      <c r="E617" s="6" t="inlineStr">
+      <c r="F617" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49362,7 +51216,10 @@
       <c r="D618" s="4">
         <v>2</v>
       </c>
-      <c r="E618" s="6" t="inlineStr">
+      <c r="E618" s="4">
+        <v>2</v>
+      </c>
+      <c r="F618" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49433,7 +51290,10 @@
       <c r="D619" s="4">
         <v>1</v>
       </c>
-      <c r="E619" s="6" t="inlineStr">
+      <c r="E619" s="4">
+        <v>1</v>
+      </c>
+      <c r="F619" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49505,7 +51365,10 @@
       <c r="D620" s="4">
         <v>1</v>
       </c>
-      <c r="E620" s="6" t="inlineStr">
+      <c r="E620" s="4">
+        <v>1</v>
+      </c>
+      <c r="F620" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49577,7 +51440,10 @@
       <c r="D621" s="4">
         <v>1</v>
       </c>
-      <c r="E621" s="6" t="inlineStr">
+      <c r="E621" s="4">
+        <v>1</v>
+      </c>
+      <c r="F621" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49647,9 +51513,12 @@
         </is>
       </c>
       <c r="D622" s="4">
+        <v>2</v>
+      </c>
+      <c r="E622" s="4">
         <v>1</v>
       </c>
-      <c r="E622" s="6" t="inlineStr">
+      <c r="F622" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49721,7 +51590,10 @@
       <c r="D623" s="4">
         <v>2</v>
       </c>
-      <c r="E623" s="6" t="inlineStr">
+      <c r="E623" s="4">
+        <v>2</v>
+      </c>
+      <c r="F623" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49791,9 +51663,12 @@
         </is>
       </c>
       <c r="D624" s="4">
+        <v>2</v>
+      </c>
+      <c r="E624" s="4">
         <v>1</v>
       </c>
-      <c r="E624" s="6" t="inlineStr">
+      <c r="F624" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49865,7 +51740,10 @@
       <c r="D625" s="4">
         <v>2</v>
       </c>
-      <c r="E625" s="6" t="inlineStr">
+      <c r="E625" s="4">
+        <v>2</v>
+      </c>
+      <c r="F625" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -49937,7 +51815,10 @@
       <c r="D626" s="4">
         <v>1</v>
       </c>
-      <c r="E626" s="6" t="inlineStr">
+      <c r="E626" s="4">
+        <v>1</v>
+      </c>
+      <c r="F626" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50009,7 +51890,10 @@
       <c r="D627" s="4">
         <v>1</v>
       </c>
-      <c r="E627" s="6" t="inlineStr">
+      <c r="E627" s="4">
+        <v>1</v>
+      </c>
+      <c r="F627" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50079,9 +51963,12 @@
         </is>
       </c>
       <c r="D628" s="4">
+        <v>2</v>
+      </c>
+      <c r="E628" s="4">
         <v>1</v>
       </c>
-      <c r="E628" s="6" t="inlineStr">
+      <c r="F628" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50153,7 +52040,10 @@
       <c r="D629" s="4">
         <v>2</v>
       </c>
-      <c r="E629" s="6" t="inlineStr">
+      <c r="E629" s="4">
+        <v>2</v>
+      </c>
+      <c r="F629" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50225,7 +52115,10 @@
       <c r="D630" s="4">
         <v>1</v>
       </c>
-      <c r="E630" s="6" t="inlineStr">
+      <c r="E630" s="4">
+        <v>1</v>
+      </c>
+      <c r="F630" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50295,9 +52188,12 @@
         </is>
       </c>
       <c r="D631" s="4">
+        <v>3</v>
+      </c>
+      <c r="E631" s="4">
         <v>1</v>
       </c>
-      <c r="E631" s="6" t="inlineStr">
+      <c r="F631" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50367,9 +52263,12 @@
         </is>
       </c>
       <c r="D632" s="4">
+        <v>3</v>
+      </c>
+      <c r="E632" s="4">
         <v>2</v>
       </c>
-      <c r="E632" s="6" t="inlineStr">
+      <c r="F632" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50441,7 +52340,10 @@
       <c r="D633" s="4">
         <v>3</v>
       </c>
-      <c r="E633" s="6" t="inlineStr">
+      <c r="E633" s="4">
+        <v>3</v>
+      </c>
+      <c r="F633" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50511,9 +52413,12 @@
         </is>
       </c>
       <c r="D634" s="4">
+        <v>2</v>
+      </c>
+      <c r="E634" s="4">
         <v>1</v>
       </c>
-      <c r="E634" s="6" t="inlineStr">
+      <c r="F634" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50585,7 +52490,10 @@
       <c r="D635" s="4">
         <v>2</v>
       </c>
-      <c r="E635" s="6" t="inlineStr">
+      <c r="E635" s="4">
+        <v>2</v>
+      </c>
+      <c r="F635" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50657,7 +52565,10 @@
       <c r="D636" s="4">
         <v>1</v>
       </c>
-      <c r="E636" s="6" t="inlineStr">
+      <c r="E636" s="4">
+        <v>1</v>
+      </c>
+      <c r="F636" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50729,7 +52640,10 @@
       <c r="D637" s="4">
         <v>1</v>
       </c>
-      <c r="E637" s="6" t="inlineStr">
+      <c r="E637" s="4">
+        <v>1</v>
+      </c>
+      <c r="F637" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50799,9 +52713,12 @@
         </is>
       </c>
       <c r="D638" s="4">
+        <v>3</v>
+      </c>
+      <c r="E638" s="4">
         <v>1</v>
       </c>
-      <c r="E638" s="6" t="inlineStr">
+      <c r="F638" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50871,9 +52788,12 @@
         </is>
       </c>
       <c r="D639" s="4">
+        <v>3</v>
+      </c>
+      <c r="E639" s="4">
         <v>2</v>
       </c>
-      <c r="E639" s="6" t="inlineStr">
+      <c r="F639" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50945,7 +52865,10 @@
       <c r="D640" s="4">
         <v>3</v>
       </c>
-      <c r="E640" s="6" t="inlineStr">
+      <c r="E640" s="4">
+        <v>3</v>
+      </c>
+      <c r="F640" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -50999,409 +52922,543 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="402">
+  <mergeCells count="536">
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
     <mergeCell ref="A40:A42"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="B63:B64"/>
     <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
     <mergeCell ref="A72:A73"/>
     <mergeCell ref="B72:B73"/>
     <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
     <mergeCell ref="A84:A88"/>
     <mergeCell ref="B84:B88"/>
     <mergeCell ref="C84:C88"/>
+    <mergeCell ref="D84:D88"/>
     <mergeCell ref="A89:A93"/>
     <mergeCell ref="B89:B93"/>
     <mergeCell ref="C89:C93"/>
+    <mergeCell ref="D89:D93"/>
     <mergeCell ref="A94:A98"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="B99:B103"/>
     <mergeCell ref="C99:C103"/>
+    <mergeCell ref="D99:D103"/>
     <mergeCell ref="A104:A108"/>
     <mergeCell ref="B104:B108"/>
     <mergeCell ref="C104:C108"/>
+    <mergeCell ref="D104:D108"/>
     <mergeCell ref="A109:A113"/>
     <mergeCell ref="B109:B113"/>
     <mergeCell ref="C109:C113"/>
+    <mergeCell ref="D109:D113"/>
     <mergeCell ref="A114:A118"/>
     <mergeCell ref="B114:B118"/>
     <mergeCell ref="C114:C118"/>
+    <mergeCell ref="D114:D118"/>
     <mergeCell ref="A119:A123"/>
     <mergeCell ref="B119:B123"/>
     <mergeCell ref="C119:C123"/>
+    <mergeCell ref="D119:D123"/>
     <mergeCell ref="A124:A128"/>
     <mergeCell ref="B124:B128"/>
     <mergeCell ref="C124:C128"/>
+    <mergeCell ref="D124:D128"/>
     <mergeCell ref="A129:A133"/>
     <mergeCell ref="B129:B133"/>
     <mergeCell ref="C129:C133"/>
+    <mergeCell ref="D129:D133"/>
     <mergeCell ref="A135:A139"/>
     <mergeCell ref="B135:B139"/>
     <mergeCell ref="C135:C139"/>
+    <mergeCell ref="D135:D139"/>
     <mergeCell ref="A140:A141"/>
     <mergeCell ref="B140:B141"/>
     <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
     <mergeCell ref="A144:A148"/>
     <mergeCell ref="B144:B148"/>
     <mergeCell ref="C144:C148"/>
+    <mergeCell ref="D144:D148"/>
     <mergeCell ref="A149:A153"/>
     <mergeCell ref="B149:B153"/>
     <mergeCell ref="C149:C153"/>
+    <mergeCell ref="D149:D153"/>
     <mergeCell ref="A154:A158"/>
     <mergeCell ref="B154:B158"/>
     <mergeCell ref="C154:C158"/>
+    <mergeCell ref="D154:D158"/>
     <mergeCell ref="A159:A163"/>
     <mergeCell ref="B159:B163"/>
     <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
     <mergeCell ref="A164:A168"/>
     <mergeCell ref="B164:B168"/>
     <mergeCell ref="C164:C168"/>
+    <mergeCell ref="D164:D168"/>
     <mergeCell ref="A169:A173"/>
     <mergeCell ref="B169:B173"/>
     <mergeCell ref="C169:C173"/>
+    <mergeCell ref="D169:D173"/>
     <mergeCell ref="A174:A178"/>
     <mergeCell ref="B174:B178"/>
     <mergeCell ref="C174:C178"/>
+    <mergeCell ref="D174:D178"/>
     <mergeCell ref="A180:A184"/>
     <mergeCell ref="B180:B184"/>
     <mergeCell ref="C180:C184"/>
+    <mergeCell ref="D180:D184"/>
     <mergeCell ref="A185:A189"/>
     <mergeCell ref="B185:B189"/>
     <mergeCell ref="C185:C189"/>
+    <mergeCell ref="D185:D189"/>
     <mergeCell ref="A191:A195"/>
     <mergeCell ref="B191:B195"/>
     <mergeCell ref="C191:C195"/>
+    <mergeCell ref="D191:D195"/>
     <mergeCell ref="A199:A203"/>
     <mergeCell ref="B199:B203"/>
     <mergeCell ref="C199:C203"/>
+    <mergeCell ref="D199:D203"/>
     <mergeCell ref="A204:A208"/>
     <mergeCell ref="B204:B208"/>
     <mergeCell ref="C204:C208"/>
+    <mergeCell ref="D204:D208"/>
     <mergeCell ref="A209:A213"/>
     <mergeCell ref="B209:B213"/>
     <mergeCell ref="C209:C213"/>
+    <mergeCell ref="D209:D213"/>
     <mergeCell ref="A214:A218"/>
     <mergeCell ref="B214:B218"/>
     <mergeCell ref="C214:C218"/>
+    <mergeCell ref="D214:D218"/>
     <mergeCell ref="A219:A223"/>
     <mergeCell ref="B219:B223"/>
     <mergeCell ref="C219:C223"/>
+    <mergeCell ref="D219:D223"/>
     <mergeCell ref="A224:A228"/>
     <mergeCell ref="B224:B228"/>
     <mergeCell ref="C224:C228"/>
+    <mergeCell ref="D224:D228"/>
     <mergeCell ref="A229:A233"/>
     <mergeCell ref="B229:B233"/>
     <mergeCell ref="C229:C233"/>
+    <mergeCell ref="D229:D233"/>
     <mergeCell ref="A234:A236"/>
     <mergeCell ref="B234:B236"/>
     <mergeCell ref="C234:C236"/>
+    <mergeCell ref="D234:D236"/>
     <mergeCell ref="A237:A241"/>
     <mergeCell ref="B237:B241"/>
     <mergeCell ref="C237:C241"/>
+    <mergeCell ref="D237:D241"/>
     <mergeCell ref="A242:A246"/>
     <mergeCell ref="B242:B246"/>
     <mergeCell ref="C242:C246"/>
+    <mergeCell ref="D242:D246"/>
     <mergeCell ref="A247:A248"/>
     <mergeCell ref="B247:B248"/>
     <mergeCell ref="C247:C248"/>
+    <mergeCell ref="D247:D248"/>
     <mergeCell ref="A249:A253"/>
     <mergeCell ref="B249:B253"/>
     <mergeCell ref="C249:C253"/>
+    <mergeCell ref="D249:D253"/>
     <mergeCell ref="A254:A256"/>
     <mergeCell ref="B254:B256"/>
     <mergeCell ref="C254:C256"/>
+    <mergeCell ref="D254:D256"/>
     <mergeCell ref="A257:A259"/>
     <mergeCell ref="B257:B259"/>
     <mergeCell ref="C257:C259"/>
+    <mergeCell ref="D257:D259"/>
     <mergeCell ref="A262:A266"/>
     <mergeCell ref="B262:B266"/>
     <mergeCell ref="C262:C266"/>
+    <mergeCell ref="D262:D266"/>
     <mergeCell ref="A267:A271"/>
     <mergeCell ref="B267:B271"/>
     <mergeCell ref="C267:C271"/>
+    <mergeCell ref="D267:D271"/>
     <mergeCell ref="A272:A276"/>
     <mergeCell ref="B272:B276"/>
     <mergeCell ref="C272:C276"/>
+    <mergeCell ref="D272:D276"/>
     <mergeCell ref="A277:A281"/>
     <mergeCell ref="B277:B281"/>
     <mergeCell ref="C277:C281"/>
+    <mergeCell ref="D277:D281"/>
     <mergeCell ref="A282:A286"/>
     <mergeCell ref="B282:B286"/>
     <mergeCell ref="C282:C286"/>
+    <mergeCell ref="D282:D286"/>
     <mergeCell ref="A287:A291"/>
     <mergeCell ref="B287:B291"/>
     <mergeCell ref="C287:C291"/>
+    <mergeCell ref="D287:D291"/>
     <mergeCell ref="A292:A296"/>
     <mergeCell ref="B292:B296"/>
     <mergeCell ref="C292:C296"/>
+    <mergeCell ref="D292:D296"/>
     <mergeCell ref="A297:A301"/>
     <mergeCell ref="B297:B301"/>
     <mergeCell ref="C297:C301"/>
+    <mergeCell ref="D297:D301"/>
     <mergeCell ref="A302:A306"/>
     <mergeCell ref="B302:B306"/>
     <mergeCell ref="C302:C306"/>
+    <mergeCell ref="D302:D306"/>
     <mergeCell ref="A307:A311"/>
     <mergeCell ref="B307:B311"/>
     <mergeCell ref="C307:C311"/>
+    <mergeCell ref="D307:D311"/>
     <mergeCell ref="A312:A316"/>
     <mergeCell ref="B312:B316"/>
     <mergeCell ref="C312:C316"/>
+    <mergeCell ref="D312:D316"/>
     <mergeCell ref="A317:A321"/>
     <mergeCell ref="B317:B321"/>
     <mergeCell ref="C317:C321"/>
+    <mergeCell ref="D317:D321"/>
     <mergeCell ref="A322:A326"/>
     <mergeCell ref="B322:B326"/>
     <mergeCell ref="C322:C326"/>
+    <mergeCell ref="D322:D326"/>
     <mergeCell ref="A327:A331"/>
     <mergeCell ref="B327:B331"/>
     <mergeCell ref="C327:C331"/>
+    <mergeCell ref="D327:D331"/>
     <mergeCell ref="A332:A336"/>
     <mergeCell ref="B332:B336"/>
     <mergeCell ref="C332:C336"/>
+    <mergeCell ref="D332:D336"/>
     <mergeCell ref="A337:A341"/>
     <mergeCell ref="B337:B341"/>
     <mergeCell ref="C337:C341"/>
+    <mergeCell ref="D337:D341"/>
     <mergeCell ref="A342:A344"/>
     <mergeCell ref="B342:B344"/>
     <mergeCell ref="C342:C344"/>
+    <mergeCell ref="D342:D344"/>
     <mergeCell ref="A345:A349"/>
     <mergeCell ref="B345:B349"/>
     <mergeCell ref="C345:C349"/>
+    <mergeCell ref="D345:D349"/>
     <mergeCell ref="A350:A353"/>
     <mergeCell ref="B350:B353"/>
     <mergeCell ref="C350:C353"/>
+    <mergeCell ref="D350:D353"/>
     <mergeCell ref="A354:A358"/>
     <mergeCell ref="B354:B358"/>
     <mergeCell ref="C354:C358"/>
+    <mergeCell ref="D354:D358"/>
     <mergeCell ref="A359:A363"/>
     <mergeCell ref="B359:B363"/>
     <mergeCell ref="C359:C363"/>
+    <mergeCell ref="D359:D363"/>
     <mergeCell ref="A364:A365"/>
     <mergeCell ref="B364:B365"/>
     <mergeCell ref="C364:C365"/>
+    <mergeCell ref="D364:D365"/>
     <mergeCell ref="A366:A370"/>
     <mergeCell ref="B366:B370"/>
     <mergeCell ref="C366:C370"/>
+    <mergeCell ref="D366:D370"/>
     <mergeCell ref="A371:A373"/>
     <mergeCell ref="B371:B373"/>
     <mergeCell ref="C371:C373"/>
+    <mergeCell ref="D371:D373"/>
     <mergeCell ref="A375:A377"/>
     <mergeCell ref="B375:B377"/>
     <mergeCell ref="C375:C377"/>
+    <mergeCell ref="D375:D377"/>
     <mergeCell ref="A380:A384"/>
     <mergeCell ref="B380:B384"/>
     <mergeCell ref="C380:C384"/>
+    <mergeCell ref="D380:D384"/>
     <mergeCell ref="A385:A389"/>
     <mergeCell ref="B385:B389"/>
     <mergeCell ref="C385:C389"/>
+    <mergeCell ref="D385:D389"/>
     <mergeCell ref="A390:A394"/>
     <mergeCell ref="B390:B394"/>
     <mergeCell ref="C390:C394"/>
+    <mergeCell ref="D390:D394"/>
     <mergeCell ref="A395:A399"/>
     <mergeCell ref="B395:B399"/>
     <mergeCell ref="C395:C399"/>
+    <mergeCell ref="D395:D399"/>
     <mergeCell ref="A400:A404"/>
     <mergeCell ref="B400:B404"/>
     <mergeCell ref="C400:C404"/>
+    <mergeCell ref="D400:D404"/>
     <mergeCell ref="A405:A409"/>
     <mergeCell ref="B405:B409"/>
     <mergeCell ref="C405:C409"/>
+    <mergeCell ref="D405:D409"/>
     <mergeCell ref="A410:A414"/>
     <mergeCell ref="B410:B414"/>
     <mergeCell ref="C410:C414"/>
+    <mergeCell ref="D410:D414"/>
     <mergeCell ref="A415:A419"/>
     <mergeCell ref="B415:B419"/>
     <mergeCell ref="C415:C419"/>
+    <mergeCell ref="D415:D419"/>
     <mergeCell ref="A420:A424"/>
     <mergeCell ref="B420:B424"/>
     <mergeCell ref="C420:C424"/>
+    <mergeCell ref="D420:D424"/>
     <mergeCell ref="A425:A429"/>
     <mergeCell ref="B425:B429"/>
     <mergeCell ref="C425:C429"/>
+    <mergeCell ref="D425:D429"/>
     <mergeCell ref="A430:A434"/>
     <mergeCell ref="B430:B434"/>
     <mergeCell ref="C430:C434"/>
+    <mergeCell ref="D430:D434"/>
     <mergeCell ref="A435:A439"/>
     <mergeCell ref="B435:B439"/>
     <mergeCell ref="C435:C439"/>
+    <mergeCell ref="D435:D439"/>
     <mergeCell ref="A440:A442"/>
     <mergeCell ref="B440:B442"/>
     <mergeCell ref="C440:C442"/>
+    <mergeCell ref="D440:D442"/>
     <mergeCell ref="A443:A446"/>
     <mergeCell ref="B443:B446"/>
     <mergeCell ref="C443:C446"/>
+    <mergeCell ref="D443:D446"/>
     <mergeCell ref="A447:A451"/>
     <mergeCell ref="B447:B451"/>
     <mergeCell ref="C447:C451"/>
+    <mergeCell ref="D447:D451"/>
     <mergeCell ref="A452:A453"/>
     <mergeCell ref="B452:B453"/>
     <mergeCell ref="C452:C453"/>
+    <mergeCell ref="D452:D453"/>
     <mergeCell ref="A454:A457"/>
     <mergeCell ref="B454:B457"/>
     <mergeCell ref="C454:C457"/>
+    <mergeCell ref="D454:D457"/>
     <mergeCell ref="A458:A461"/>
     <mergeCell ref="B458:B461"/>
     <mergeCell ref="C458:C461"/>
+    <mergeCell ref="D458:D461"/>
     <mergeCell ref="A463:A466"/>
     <mergeCell ref="B463:B466"/>
     <mergeCell ref="C463:C466"/>
+    <mergeCell ref="D463:D466"/>
     <mergeCell ref="A467:A468"/>
     <mergeCell ref="B467:B468"/>
     <mergeCell ref="C467:C468"/>
+    <mergeCell ref="D467:D468"/>
     <mergeCell ref="A472:A473"/>
     <mergeCell ref="B472:B473"/>
     <mergeCell ref="C472:C473"/>
+    <mergeCell ref="D472:D473"/>
     <mergeCell ref="A475:A479"/>
     <mergeCell ref="B475:B479"/>
     <mergeCell ref="C475:C479"/>
+    <mergeCell ref="D475:D479"/>
     <mergeCell ref="A480:A484"/>
     <mergeCell ref="B480:B484"/>
     <mergeCell ref="C480:C484"/>
+    <mergeCell ref="D480:D484"/>
     <mergeCell ref="A485:A489"/>
     <mergeCell ref="B485:B489"/>
     <mergeCell ref="C485:C489"/>
+    <mergeCell ref="D485:D489"/>
     <mergeCell ref="A490:A494"/>
     <mergeCell ref="B490:B494"/>
     <mergeCell ref="C490:C494"/>
+    <mergeCell ref="D490:D494"/>
     <mergeCell ref="A495:A499"/>
     <mergeCell ref="B495:B499"/>
     <mergeCell ref="C495:C499"/>
+    <mergeCell ref="D495:D499"/>
     <mergeCell ref="A500:A504"/>
     <mergeCell ref="B500:B504"/>
     <mergeCell ref="C500:C504"/>
+    <mergeCell ref="D500:D504"/>
     <mergeCell ref="A505:A509"/>
     <mergeCell ref="B505:B509"/>
     <mergeCell ref="C505:C509"/>
+    <mergeCell ref="D505:D509"/>
     <mergeCell ref="A510:A514"/>
     <mergeCell ref="B510:B514"/>
     <mergeCell ref="C510:C514"/>
+    <mergeCell ref="D510:D514"/>
     <mergeCell ref="A515:A519"/>
     <mergeCell ref="B515:B519"/>
     <mergeCell ref="C515:C519"/>
+    <mergeCell ref="D515:D519"/>
     <mergeCell ref="A520:A524"/>
     <mergeCell ref="B520:B524"/>
     <mergeCell ref="C520:C524"/>
+    <mergeCell ref="D520:D524"/>
     <mergeCell ref="A525:A529"/>
     <mergeCell ref="B525:B529"/>
     <mergeCell ref="C525:C529"/>
+    <mergeCell ref="D525:D529"/>
     <mergeCell ref="A530:A534"/>
     <mergeCell ref="B530:B534"/>
     <mergeCell ref="C530:C534"/>
+    <mergeCell ref="D530:D534"/>
     <mergeCell ref="A535:A539"/>
     <mergeCell ref="B535:B539"/>
     <mergeCell ref="C535:C539"/>
+    <mergeCell ref="D535:D539"/>
     <mergeCell ref="A540:A542"/>
     <mergeCell ref="B540:B542"/>
     <mergeCell ref="C540:C542"/>
+    <mergeCell ref="D540:D542"/>
     <mergeCell ref="A543:A547"/>
     <mergeCell ref="B543:B547"/>
     <mergeCell ref="C543:C547"/>
+    <mergeCell ref="D543:D547"/>
     <mergeCell ref="A553:A555"/>
     <mergeCell ref="B553:B555"/>
     <mergeCell ref="C553:C555"/>
+    <mergeCell ref="D553:D555"/>
     <mergeCell ref="A558:A559"/>
     <mergeCell ref="B558:B559"/>
     <mergeCell ref="C558:C559"/>
+    <mergeCell ref="D558:D559"/>
     <mergeCell ref="A563:A564"/>
     <mergeCell ref="B563:B564"/>
     <mergeCell ref="C563:C564"/>
+    <mergeCell ref="D563:D564"/>
     <mergeCell ref="A565:A566"/>
     <mergeCell ref="B565:B566"/>
     <mergeCell ref="C565:C566"/>
+    <mergeCell ref="D565:D566"/>
     <mergeCell ref="A569:A575"/>
     <mergeCell ref="B569:B575"/>
     <mergeCell ref="C569:C575"/>
+    <mergeCell ref="D569:D575"/>
     <mergeCell ref="A578:A580"/>
     <mergeCell ref="B578:B580"/>
     <mergeCell ref="C578:C580"/>
+    <mergeCell ref="D578:D580"/>
     <mergeCell ref="A583:A584"/>
     <mergeCell ref="B583:B584"/>
     <mergeCell ref="C583:C584"/>
+    <mergeCell ref="D583:D584"/>
     <mergeCell ref="A586:A587"/>
     <mergeCell ref="B586:B587"/>
     <mergeCell ref="C586:C587"/>
+    <mergeCell ref="D586:D587"/>
     <mergeCell ref="A588:A589"/>
     <mergeCell ref="B588:B589"/>
     <mergeCell ref="C588:C589"/>
+    <mergeCell ref="D588:D589"/>
     <mergeCell ref="A590:A592"/>
     <mergeCell ref="B590:B592"/>
     <mergeCell ref="C590:C592"/>
+    <mergeCell ref="D590:D592"/>
     <mergeCell ref="A594:A596"/>
     <mergeCell ref="B594:B596"/>
     <mergeCell ref="C594:C596"/>
+    <mergeCell ref="D594:D596"/>
     <mergeCell ref="A597:A599"/>
     <mergeCell ref="B597:B599"/>
     <mergeCell ref="C597:C599"/>
+    <mergeCell ref="D597:D599"/>
     <mergeCell ref="A600:A604"/>
     <mergeCell ref="B600:B604"/>
     <mergeCell ref="C600:C604"/>
+    <mergeCell ref="D600:D604"/>
     <mergeCell ref="A608:A609"/>
     <mergeCell ref="B608:B609"/>
     <mergeCell ref="C608:C609"/>
+    <mergeCell ref="D608:D609"/>
     <mergeCell ref="A610:A616"/>
     <mergeCell ref="B610:B616"/>
     <mergeCell ref="C610:C616"/>
+    <mergeCell ref="D610:D616"/>
     <mergeCell ref="A617:A618"/>
     <mergeCell ref="B617:B618"/>
     <mergeCell ref="C617:C618"/>
+    <mergeCell ref="D617:D618"/>
     <mergeCell ref="A622:A623"/>
     <mergeCell ref="B622:B623"/>
     <mergeCell ref="C622:C623"/>
+    <mergeCell ref="D622:D623"/>
     <mergeCell ref="A624:A625"/>
     <mergeCell ref="B624:B625"/>
     <mergeCell ref="C624:C625"/>
+    <mergeCell ref="D624:D625"/>
     <mergeCell ref="A628:A629"/>
     <mergeCell ref="B628:B629"/>
     <mergeCell ref="C628:C629"/>
+    <mergeCell ref="D628:D629"/>
     <mergeCell ref="A631:A633"/>
     <mergeCell ref="B631:B633"/>
     <mergeCell ref="C631:C633"/>
+    <mergeCell ref="D631:D633"/>
     <mergeCell ref="A634:A635"/>
     <mergeCell ref="B634:B635"/>
     <mergeCell ref="C634:C635"/>
+    <mergeCell ref="D634:D635"/>
     <mergeCell ref="A638:A640"/>
     <mergeCell ref="B638:B640"/>
     <mergeCell ref="C638:C640"/>
+    <mergeCell ref="D638:D640"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
